--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100565</v>
+        <v>100567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92682</v>
+        <v>92684</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92682</v>
+        <v>92684</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100565</v>
+        <v>100567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92293</v>
+        <v>92295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1845,6 +1845,218 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128575633</v>
+      </c>
+      <c r="B14" t="n">
+        <v>89431</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ramdalen, Dls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>346628</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6529509</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128575795</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92446</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ramdalen, Dls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>346628</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6529509</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg, David Göransson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92684</v>
+        <v>92776</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100567</v>
+        <v>100660</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92295</v>
+        <v>92387</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100660</v>
+        <v>100668</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92776</v>
+        <v>92782</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100660</v>
+        <v>100668</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92387</v>
+        <v>92393</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89431</v>
+        <v>89437</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92446</v>
+        <v>92452</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92782</v>
+        <v>92788</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100668</v>
+        <v>100674</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92393</v>
+        <v>92399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89437</v>
+        <v>89443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92452</v>
+        <v>92458</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92788</v>
+        <v>92790</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100674</v>
+        <v>100679</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89443</v>
+        <v>89445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92458</v>
+        <v>92460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100679</v>
+        <v>100685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92790</v>
+        <v>92791</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100685</v>
+        <v>100686</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92401</v>
+        <v>92402</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92460</v>
+        <v>92461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89445</v>
+        <v>89472</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92461</v>
+        <v>92488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92791</v>
+        <v>92818</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100686</v>
+        <v>100713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89472</v>
+        <v>89477</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92488</v>
+        <v>92493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100713</v>
+        <v>100726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92818</v>
+        <v>92830</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100713</v>
+        <v>100726</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92429</v>
+        <v>92439</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89477</v>
+        <v>89482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92493</v>
+        <v>92498</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89482</v>
+        <v>89486</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92498</v>
+        <v>92502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92830</v>
+        <v>92834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100726</v>
+        <v>100730</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92439</v>
+        <v>92443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128465407</v>
       </c>
       <c r="B2" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128465406</v>
       </c>
       <c r="B3" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128465394</v>
       </c>
       <c r="B4" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128465403</v>
       </c>
       <c r="B5" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128465405</v>
       </c>
       <c r="B6" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128465408</v>
       </c>
       <c r="B7" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128465401</v>
       </c>
       <c r="B8" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128465399</v>
       </c>
       <c r="B9" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>128465400</v>
       </c>
       <c r="B10" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>128465409</v>
       </c>
       <c r="B12" t="n">
-        <v>100730</v>
+        <v>100737</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92443</v>
+        <v>92448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89486</v>
+        <v>89491</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92502</v>
+        <v>92507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89493</v>
+        <v>89498</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92510</v>
+        <v>92515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -1850,7 +1850,7 @@
         <v>128575633</v>
       </c>
       <c r="B14" t="n">
-        <v>89498</v>
+        <v>89504</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>128575795</v>
       </c>
       <c r="B15" t="n">
-        <v>92515</v>
+        <v>92523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128465407</v>
+        <v>17038189</v>
       </c>
       <c r="B2" t="n">
-        <v>92451</v>
+        <v>88984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4769</v>
+        <v>372</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gråbrun ängsfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Clavulinopsis umbrinella</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Sacc.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Dackehögen N, Dls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346628</v>
+        <v>346601</v>
       </c>
       <c r="R2" t="n">
-        <v>6529502</v>
+        <v>6529562</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +742,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2014-09-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2014-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,66 +756,75 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Rik barrskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anita Stridvall</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anita Stridvall, Jan  Olsson, Stig Jacobsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128465406</v>
+        <v>128576554</v>
       </c>
       <c r="B3" t="n">
-        <v>100740</v>
+        <v>83298</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>492</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Ramdalen, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>346635</v>
+        <v>346568</v>
       </c>
       <c r="R3" t="n">
-        <v>6529495</v>
+        <v>6529548</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -837,12 +848,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Upptäckt av David Göransson.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -851,66 +867,81 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128465394</v>
+        <v>422177</v>
       </c>
       <c r="B4" t="n">
-        <v>92451</v>
+        <v>101947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>1449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Hällebräcka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Saxifraga osloënsis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Knaben</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Ramdalen, 600 m VSV om, vägskärning, Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>346745</v>
+        <v>346774</v>
       </c>
       <c r="R4" t="n">
-        <v>6529486</v>
+        <v>6529551</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -932,14 +963,24 @@
           <t>Tisselskog</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>OD-Ben-0182</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2001-01-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2001-12-31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 m2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -950,64 +991,73 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Sydvänd vägskärning på enskilda vägen till Ramdalen</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Dalsland Floraväktarna</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Anders Bertilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128465403</v>
+        <v>17038190</v>
       </c>
       <c r="B5" t="n">
-        <v>92451</v>
+        <v>93205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4769</v>
+        <v>2058</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Dackehögen N, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>346702</v>
+        <v>346568</v>
       </c>
       <c r="R5" t="n">
-        <v>6529481</v>
+        <v>6529504</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1031,12 +1081,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2014-09-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2014-09-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1047,26 +1097,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Rik barrskog</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anita Stridvall</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Anita Stridvall, Jan  Olsson, Stig Jacobsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128465405</v>
+        <v>128576275</v>
       </c>
       <c r="B6" t="n">
-        <v>92451</v>
+        <v>96437</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1129,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>2667</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Ramdalen, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>346642</v>
+        <v>346568</v>
       </c>
       <c r="R6" t="n">
-        <v>6529504</v>
+        <v>6529548</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1128,12 +1187,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1142,28 +1201,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joakim Andersson Hemberg, David Göransson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128465408</v>
+        <v>128576207</v>
       </c>
       <c r="B7" t="n">
-        <v>92451</v>
+        <v>96186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1236,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>2676</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+          <t>Ramdalen, Dls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>346613</v>
+        <v>346568</v>
       </c>
       <c r="R7" t="n">
-        <v>6529506</v>
+        <v>6529548</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1225,12 +1294,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1239,28 +1308,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Joakim Andersson Hemberg, David Göransson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128465401</v>
+        <v>128465389</v>
       </c>
       <c r="B8" t="n">
-        <v>92451</v>
+        <v>92869</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1367,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>346726</v>
+        <v>346718</v>
       </c>
       <c r="R8" t="n">
-        <v>6529493</v>
+        <v>6529597</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1354,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128465399</v>
+        <v>128465394</v>
       </c>
       <c r="B9" t="n">
-        <v>92842</v>
+        <v>92869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,37 +1440,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Norr om Dackehöjdens naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>346734</v>
+        <v>346745</v>
       </c>
       <c r="R9" t="n">
-        <v>6529452</v>
+        <v>6529486</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1436,7 +1508,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1455,10 +1526,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128465400</v>
+        <v>128465401</v>
       </c>
       <c r="B10" t="n">
-        <v>92842</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1466,37 +1537,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Norr om Dackehöjdens naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>346722</v>
+        <v>346726</v>
       </c>
       <c r="R10" t="n">
-        <v>6529482</v>
+        <v>6529493</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1537,7 +1605,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1559,7 +1626,7 @@
         <v>128465402</v>
       </c>
       <c r="B11" t="n">
-        <v>92451</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128465409</v>
+        <v>128465403</v>
       </c>
       <c r="B12" t="n">
-        <v>100740</v>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1664,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1688,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>346609</v>
+        <v>346702</v>
       </c>
       <c r="R12" t="n">
-        <v>6529508</v>
+        <v>6529481</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1753,7 +1820,7 @@
         <v>128465404</v>
       </c>
       <c r="B13" t="n">
-        <v>92451</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128575633</v>
+        <v>128465405</v>
       </c>
       <c r="B14" t="n">
-        <v>89504</v>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1858,40 +1925,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>236437</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brun klibbskivling</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Limacella glioderma</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Maire</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ramdalen, Dls</t>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>346628</v>
+        <v>346642</v>
       </c>
       <c r="R14" t="n">
-        <v>6529509</v>
+        <v>6529504</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1915,12 +1979,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1929,34 +1993,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joakim Andersson Hemberg</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128575795</v>
+        <v>128465407</v>
       </c>
       <c r="B15" t="n">
-        <v>92523</v>
+        <v>92869</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1964,40 +2022,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5836</v>
+        <v>4769</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ramdalen, Dls</t>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q15" t="n">
         <v>346628</v>
       </c>
       <c r="R15" t="n">
-        <v>6529509</v>
+        <v>6529502</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2021,12 +2076,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2035,27 +2090,1555 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128465408</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>346613</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6529506</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128575795</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92928</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5836</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Guldkremla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Russula aurea</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ramdalen, Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>346628</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6529509</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
           <t>Joakim Andersson Hemberg</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX17" t="inlineStr">
         <is>
           <t>Joakim Andersson Hemberg, David Göransson</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128465388</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>346641</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6529572</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128465390</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>346741</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6529587</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128465391</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>346754</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6529578</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128465393</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>346765</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6529577</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128465399</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>346734</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6529452</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128465400</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>346722</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6529482</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129042401</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Dackehögen, Dls</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>346582</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6529463</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2010-01-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2010-01-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Svante Hultengren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Svante Hultengren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128578767</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58067</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100090</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Nötkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Nucifraga caryocatactes</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ramdalen, Dls</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>346568</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6529548</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128465397</v>
+      </c>
+      <c r="B26" t="n">
+        <v>111390</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>346726</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6529387</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128465410</v>
+      </c>
+      <c r="B27" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>346597</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6529541</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128465406</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>346635</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6529495</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128465409</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norr om Dackehöjdens naturreservat, Dls</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>346609</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6529508</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128575633</v>
+      </c>
+      <c r="B30" t="n">
+        <v>89870</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>236437</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Brun klibbskivling</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Limacella glioderma</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Maire</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ramdalen, Dls</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>346628</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6529509</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joakim Andersson Hemberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -3046,7 +3046,7 @@
         <v>128578767</v>
       </c>
       <c r="B25" t="n">
-        <v>58067</v>
+        <v>58089</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17038189</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128576554</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/422177</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17038190</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128576275</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128576207</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465389</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1523,6 +1563,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465394</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1620,6 +1665,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465401</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1717,6 +1767,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465402</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1814,6 +1869,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465403</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1911,6 +1971,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465404</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2008,6 +2073,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465405</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2105,6 +2175,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465407</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465408</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2308,6 +2388,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128575795</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465388</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2510,6 +2600,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465390</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2611,6 +2706,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465391</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2712,6 +2812,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465393</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2813,6 +2918,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465399</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2914,6 +3024,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465400</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3040,6 +3155,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129042401</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3145,6 +3265,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128578767</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3242,6 +3367,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465397</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3339,6 +3469,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465410</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3436,6 +3571,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465406</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3533,6 +3673,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128465409</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3639,8 +3784,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128575633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 40237-2025 artfynd.xlsx
+++ b/artfynd/A 40237-2025 artfynd.xlsx
@@ -3166,7 +3166,7 @@
         <v>128578767</v>
       </c>
       <c r="B25" t="n">
-        <v>58089</v>
+        <v>58094</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
